--- a/output/yearly_surface_area_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_83_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497622792134</v>
+        <v>10.84497626916771</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890715785004</v>
+        <v>37.78907172222246</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.82332647096458</v>
+        <v>6.232134426558751</v>
       </c>
       <c r="C2" t="n">
-        <v>4.342270095883642</v>
+        <v>7.134360566761572</v>
       </c>
       <c r="D2" t="n">
-        <v>29.53489793456104</v>
+        <v>22.72451411020092</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.07259257685203</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="C3" t="n">
-        <v>23.94482650657971</v>
+        <v>36.01541453029424</v>
       </c>
       <c r="D3" t="n">
-        <v>68.42290624748145</v>
+        <v>62.70422587024377</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.3354642818787</v>
+        <v>38.02014334236623</v>
       </c>
       <c r="C4" t="n">
-        <v>85.44641143912114</v>
+        <v>65.08987279156354</v>
       </c>
       <c r="D4" t="n">
-        <v>76.67842269249287</v>
+        <v>101.106269069562</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.58392856651115</v>
+        <v>50.31456984264904</v>
       </c>
       <c r="C5" t="n">
-        <v>131.1614932873739</v>
+        <v>123.970191353766</v>
       </c>
       <c r="D5" t="n">
-        <v>51.0999680060465</v>
+        <v>79.03069019186825</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.30449032369931</v>
+        <v>45.68562941712533</v>
       </c>
       <c r="C6" t="n">
-        <v>98.53605357984388</v>
+        <v>145.831749231934</v>
       </c>
       <c r="D6" t="n">
-        <v>39.32586778901449</v>
+        <v>52.08564270111029</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.54217107911827</v>
+        <v>30.9014907388726</v>
       </c>
       <c r="C7" t="n">
-        <v>61.08434215823654</v>
+        <v>121.0907253372101</v>
       </c>
       <c r="D7" t="n">
-        <v>37.96811071404115</v>
+        <v>40.3036885024443</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.02212253330794</v>
+        <v>15.52143120414207</v>
       </c>
       <c r="C8" t="n">
-        <v>40.47254910757476</v>
+        <v>78.27474445959818</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>29.84218496599028</v>
+        <v>43.93124626963626</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.736062974415211</v>
+        <v>7.65394637898884</v>
       </c>
       <c r="C21" t="n">
-        <v>96.70078718019015</v>
+        <v>92.80409984523968</v>
       </c>
       <c r="D21" t="n">
-        <v>8.703070846217113</v>
+        <v>7.65394637898884</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.744025891098841</v>
+        <v>7.655668597716628</v>
       </c>
       <c r="C2" t="n">
-        <v>6.235079669671493</v>
+        <v>8.93488585635022</v>
       </c>
       <c r="D2" t="n">
-        <v>23.53641946161303</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.58662746324986</v>
+        <v>18.61393647251952</v>
       </c>
       <c r="C3" t="n">
-        <v>20.06201433628357</v>
+        <v>31.67608967752334</v>
       </c>
       <c r="D3" t="n">
-        <v>75.12333432896592</v>
+        <v>65.10459900712723</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.21685273611408</v>
+        <v>34.74012426247764</v>
       </c>
       <c r="C4" t="n">
-        <v>72.0838434366178</v>
+        <v>76.257252927371</v>
       </c>
       <c r="D4" t="n">
-        <v>91.82777151672541</v>
+        <v>106.5687132959913</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.82998738737862</v>
+        <v>53.11255079975246</v>
       </c>
       <c r="C5" t="n">
-        <v>143.0897278939727</v>
+        <v>121.9330648674539</v>
       </c>
       <c r="D5" t="n">
-        <v>64.77080478768333</v>
+        <v>94.34595437811849</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.04539104523617</v>
+        <v>55.94980166502573</v>
       </c>
       <c r="C6" t="n">
-        <v>152.3525174835413</v>
+        <v>167.8494049950772</v>
       </c>
       <c r="D6" t="n">
-        <v>46.0478943199924</v>
+        <v>62.02780170201773</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.12402867256714</v>
+        <v>41.14210104187108</v>
       </c>
       <c r="C7" t="n">
-        <v>99.83097880174539</v>
+        <v>162.3525995989993</v>
       </c>
       <c r="D7" t="n">
-        <v>40.78278138211675</v>
+        <v>45.33416373900496</v>
       </c>
     </row>
     <row r="8">
@@ -1175,10 +1175,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.36697801940583</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>60.50020227420968</v>
+        <v>114.658314378985</v>
       </c>
       <c r="D8" t="n">
         <v>37.80219535202343</v>
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.87031149204818</v>
+        <v>11.20468654856884</v>
       </c>
       <c r="C9" t="n">
-        <v>39.82655911818034</v>
+        <v>67.56093176315272</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.925433535893582</v>
+        <v>7.826688126649962</v>
       </c>
       <c r="C21" t="n">
-        <v>106.0026735425767</v>
+        <v>100.7686096306183</v>
       </c>
       <c r="D21" t="n">
-        <v>9.906791919866977</v>
+        <v>8.805024142481209</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.081747101359742</v>
+        <v>7.910923000820798</v>
       </c>
       <c r="C2" t="n">
-        <v>8.465610453720245</v>
+        <v>14.83028082035232</v>
       </c>
       <c r="D2" t="n">
-        <v>22.44569776219483</v>
+        <v>28.75048151886784</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.86704745376596</v>
+        <v>21.47573103039898</v>
       </c>
       <c r="C3" t="n">
-        <v>21.98623983660732</v>
+        <v>32.7511034136736</v>
       </c>
       <c r="D3" t="n">
-        <v>75.63875187369551</v>
+        <v>70.94599784739574</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.76190263842031</v>
+        <v>34.07646281440679</v>
       </c>
       <c r="C4" t="n">
-        <v>61.40144666670826</v>
+        <v>77.23998237932204</v>
       </c>
       <c r="D4" t="n">
-        <v>104.04169470526</v>
+        <v>112.3502255263007</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.87907477259096</v>
+        <v>52.30260894374884</v>
       </c>
       <c r="C5" t="n">
-        <v>136.7574552015807</v>
+        <v>128.1671627894211</v>
       </c>
       <c r="D5" t="n">
-        <v>79.96335051090271</v>
+        <v>105.4151597435013</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.25043744670351</v>
+        <v>61.98755004614362</v>
       </c>
       <c r="C6" t="n">
-        <v>186.4456700089203</v>
+        <v>177.3890474372435</v>
       </c>
       <c r="D6" t="n">
-        <v>53.61520562432682</v>
+        <v>73.05675541152641</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.82565948593412</v>
+        <v>51.2030515149924</v>
       </c>
       <c r="C7" t="n">
-        <v>152.2317625159189</v>
+        <v>194.9309154167254</v>
       </c>
       <c r="D7" t="n">
-        <v>44.43586458961913</v>
+        <v>51.26293812495145</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.12907627980861</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="C8" t="n">
-        <v>92.79479300540851</v>
+        <v>157.2170773580842</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.30624853046277</v>
+        <v>16.19687362466387</v>
       </c>
       <c r="C9" t="n">
-        <v>55.24687030878498</v>
+        <v>97.62499171030279</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>39.43189654107314</v>
+        <v>56.51430659496764</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7169632282032</v>
+        <v>38.56010457970196</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>31.73990327829938</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.09930787644454</v>
+        <v>7.983208760717872</v>
       </c>
       <c r="C21" t="n">
-        <v>114.4027237547791</v>
+        <v>107.7733182696913</v>
       </c>
       <c r="D21" t="n">
-        <v>11.13654833011124</v>
+        <v>9.97901095089734</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.32874661220244</v>
+        <v>7.324819621385452</v>
       </c>
       <c r="C2" t="n">
-        <v>5.62050560681299</v>
+        <v>10.32111361474672</v>
       </c>
       <c r="D2" t="n">
-        <v>18.35770032171111</v>
+        <v>23.68073637413731</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.24425955637498</v>
+        <v>24.51914891356409</v>
       </c>
       <c r="C3" t="n">
-        <v>36.15776794741003</v>
+        <v>51.69883410563704</v>
       </c>
       <c r="D3" t="n">
-        <v>82.51098580342318</v>
+        <v>77.97531140980291</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.44060909722434</v>
+        <v>25.12979598560561</v>
       </c>
       <c r="C4" t="n">
-        <v>103.0462025331537</v>
+        <v>105.4966448029537</v>
       </c>
       <c r="D4" t="n">
-        <v>97.25192758268904</v>
+        <v>111.2271061526424</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.37942194439156</v>
+        <v>34.90113088597411</v>
       </c>
       <c r="C5" t="n">
-        <v>111.4038207394068</v>
+        <v>105.9796646734432</v>
       </c>
       <c r="D5" t="n">
-        <v>54.29064804484862</v>
+        <v>71.98665041389738</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.91327171132357</v>
+        <v>31.79880814055419</v>
       </c>
       <c r="C6" t="n">
-        <v>100.266874782431</v>
+        <v>128.3625305825663</v>
       </c>
       <c r="D6" t="n">
-        <v>29.26295382048468</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.91849924501429</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="C7" t="n">
-        <v>65.21651824541136</v>
+        <v>110.5506819844163</v>
       </c>
       <c r="D7" t="n">
-        <v>27.84727363096077</v>
+        <v>28.26647990067416</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>40.72289477215769</v>
+        <v>71.9326542901638</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.06405994715006</v>
+        <v>43.15468383557703</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.426700398448868</v>
+        <v>4.478733026773948</v>
       </c>
       <c r="C2" t="n">
-        <v>2.685079971115026</v>
+        <v>4.76442160870977</v>
       </c>
       <c r="D2" t="n">
-        <v>14.11949548247763</v>
+        <v>16.60528066963055</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.53034904893831</v>
+        <v>25.42235680147115</v>
       </c>
       <c r="C3" t="n">
-        <v>29.27080780211865</v>
+        <v>46.94226647856124</v>
       </c>
       <c r="D3" t="n">
-        <v>79.75227475448963</v>
+        <v>79.72773106188347</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.52315801983909</v>
+        <v>34.19132729580366</v>
       </c>
       <c r="C4" t="n">
-        <v>99.52369177031616</v>
+        <v>119.3824843318206</v>
       </c>
       <c r="D4" t="n">
-        <v>113.2308532170101</v>
+        <v>122.0881810047248</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.01188845010476</v>
+        <v>38.23907308041327</v>
       </c>
       <c r="C5" t="n">
-        <v>151.9009135395877</v>
+        <v>147.9248353373882</v>
       </c>
       <c r="D5" t="n">
-        <v>72.03573779910973</v>
+        <v>89.55993431991529</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.47429161880501</v>
+        <v>37.27303333943441</v>
       </c>
       <c r="C6" t="n">
-        <v>136.4128617573901</v>
+        <v>151.4669810543107</v>
       </c>
       <c r="D6" t="n">
-        <v>35.50196048097316</v>
+        <v>41.57996051796516</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.72076704583318</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="C7" t="n">
-        <v>94.14175085563514</v>
+        <v>139.6555744245173</v>
       </c>
       <c r="D7" t="n">
-        <v>30.12296480940488</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>56.16087742143878</v>
+        <v>96.04928664498669</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>36.0546844384641</v>
+        <v>47.03749600587317</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.510148953309847</v>
+        <v>4.64464838879166</v>
       </c>
       <c r="C2" t="n">
-        <v>3.216205479112551</v>
+        <v>5.067781649322035</v>
       </c>
       <c r="D2" t="n">
-        <v>14.08415256512474</v>
+        <v>13.13971127363931</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.18473279931442</v>
+        <v>20.51852701875834</v>
       </c>
       <c r="C3" t="n">
-        <v>19.00663555421825</v>
+        <v>32.05897128217959</v>
       </c>
       <c r="D3" t="n">
-        <v>72.94385442553801</v>
+        <v>74.8140838021282</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.96382387032566</v>
+        <v>40.58545009356314</v>
       </c>
       <c r="C4" t="n">
-        <v>85.5357504802076</v>
+        <v>118.1700259170758</v>
       </c>
       <c r="D4" t="n">
-        <v>126.0446242528395</v>
+        <v>132.2728316885812</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.1541029985003</v>
+        <v>44.25227776892498</v>
       </c>
       <c r="C5" t="n">
-        <v>169.523284830818</v>
+        <v>183.8813450054276</v>
       </c>
       <c r="D5" t="n">
-        <v>93.60964359993338</v>
+        <v>109.121257327033</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.59254331167113</v>
+        <v>44.03531152628644</v>
       </c>
       <c r="C6" t="n">
-        <v>186.9689415352838</v>
+        <v>189.384040887731</v>
       </c>
       <c r="D6" t="n">
-        <v>47.69821221083129</v>
+        <v>56.19131160027045</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.9014907388726</v>
+        <v>28.98511922018283</v>
       </c>
       <c r="C7" t="n">
-        <v>144.0272969515283</v>
+        <v>177.0248190389678</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.93729132011522</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C8" t="n">
-        <v>88.28857104291565</v>
+        <v>135.5204530942297</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>51.47499562906875</v>
+        <v>76.65780599070366</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>37.15424186722054</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.29272504678157</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>26.53664044579129</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.630102099677205</v>
+        <v>2.797980957103409</v>
       </c>
       <c r="C2" t="n">
-        <v>1.474585051778709</v>
+        <v>2.422953334081128</v>
       </c>
       <c r="D2" t="n">
-        <v>9.725192758268904</v>
+        <v>9.173450548482196</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.20927649192059</v>
+        <v>20.58234061953438</v>
       </c>
       <c r="C3" t="n">
-        <v>17.33766445699867</v>
+        <v>28.92719610563227</v>
       </c>
       <c r="D3" t="n">
-        <v>70.90672793922589</v>
+        <v>72.18790869326797</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.48182680526948</v>
+        <v>44.49084246105696</v>
       </c>
       <c r="C4" t="n">
-        <v>79.47345840648354</v>
+        <v>116.0258889310008</v>
       </c>
       <c r="D4" t="n">
-        <v>134.3659177940355</v>
+        <v>140.517548908846</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.28940425523712</v>
+        <v>46.43666641087414</v>
       </c>
       <c r="C5" t="n">
-        <v>193.6988220478957</v>
+        <v>223.2003405605124</v>
       </c>
       <c r="D5" t="n">
-        <v>102.0035864712436</v>
+        <v>114.7172192412398</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.71580155404972</v>
+        <v>35.46170882509904</v>
       </c>
       <c r="C6" t="n">
-        <v>223.9602132835994</v>
+        <v>223.7992066601029</v>
       </c>
       <c r="D6" t="n">
-        <v>47.2956956520901</v>
+        <v>54.70200033292804</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.881290643244144</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>138.9369351050086</v>
+        <v>181.2168817361017</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>66.42504966933919</v>
+        <v>96.29963230956963</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>28.28906009787183</v>
+        <v>32.28280975874785</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.50125647070939</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.66584592765759</v>
+        <v>3.363467634749572</v>
       </c>
       <c r="C2" t="n">
-        <v>5.343652754215388</v>
+        <v>4.565126824747668</v>
       </c>
       <c r="D2" t="n">
-        <v>10.25435477085793</v>
+        <v>10.43205110532661</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.68203691701105</v>
+        <v>15.34471661737765</v>
       </c>
       <c r="C3" t="n">
-        <v>11.22137625954104</v>
+        <v>19.18825887950391</v>
       </c>
       <c r="D3" t="n">
-        <v>63.4994415106837</v>
+        <v>64.44682804528188</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.30390948662256</v>
+        <v>41.96382387032566</v>
       </c>
       <c r="C4" t="n">
-        <v>60.98027690158638</v>
+        <v>95.91184196639215</v>
       </c>
       <c r="D4" t="n">
-        <v>138.437225523547</v>
+        <v>143.4912627050096</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.81864838328416</v>
+        <v>55.10058990085224</v>
       </c>
       <c r="C5" t="n">
-        <v>172.2967220953152</v>
+        <v>218.5124952727339</v>
       </c>
       <c r="D5" t="n">
-        <v>122.9148125717007</v>
+        <v>133.6158625479909</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.22148373719484</v>
+        <v>46.0478943199924</v>
       </c>
       <c r="C6" t="n">
-        <v>267.5527565952705</v>
+        <v>284.8609686211418</v>
       </c>
       <c r="D6" t="n">
-        <v>64.40264939859078</v>
+        <v>72.45298057341462</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4992929753009</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C7" t="n">
-        <v>220.2030648194468</v>
+        <v>240.8639452553209</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>116.9114253602314</v>
+        <v>153.2115467247572</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>49.03437083631118</v>
+        <v>63.23436963053704</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.23287949455151</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41654843070368</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.765583282863265</v>
+        <v>2.276672926148354</v>
       </c>
       <c r="C2" t="n">
-        <v>3.171045084717197</v>
+        <v>4.092906179004952</v>
       </c>
       <c r="D2" t="n">
-        <v>7.446556336712057</v>
+        <v>8.779769719079225</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.93099992326224</v>
+        <v>13.85246010692249</v>
       </c>
       <c r="C3" t="n">
-        <v>16.07611865704152</v>
+        <v>18.71701998146544</v>
       </c>
       <c r="D3" t="n">
-        <v>58.98340207114836</v>
+        <v>59.6657167255999</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.44131310748811</v>
+        <v>38.09671966329748</v>
       </c>
       <c r="C4" t="n">
-        <v>48.02611594404971</v>
+        <v>78.55454255530854</v>
       </c>
       <c r="D4" t="n">
-        <v>139.1391751320834</v>
+        <v>143.5040254251647</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.16917337142928</v>
+        <v>59.22393025868885</v>
       </c>
       <c r="C5" t="n">
-        <v>153.0544670920778</v>
+        <v>208.4741249968102</v>
       </c>
       <c r="D5" t="n">
-        <v>138.0337272171016</v>
+        <v>147.1394371739907</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.63407981488576</v>
+        <v>53.61520562432682</v>
       </c>
       <c r="C6" t="n">
-        <v>283.6131672890441</v>
+        <v>318.7931145230243</v>
       </c>
       <c r="D6" t="n">
-        <v>76.71965609607126</v>
+        <v>84.24671574453156</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.84054026575129</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="C7" t="n">
-        <v>282.2455927370282</v>
+        <v>300.2714623347039</v>
       </c>
       <c r="D7" t="n">
-        <v>42.63926629084747</v>
+        <v>44.49575119957818</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>162.8915790886308</v>
+        <v>196.2710010330223</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>60.23905738488002</v>
+        <v>71.55468142402876</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.793874039837175</v>
+        <v>3.171045084717197</v>
       </c>
       <c r="C2" t="n">
-        <v>4.828235209485814</v>
+        <v>6.49131582047991</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02150063850219</v>
+        <v>10.07567668868501</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.67788894201581</v>
+        <v>10.94648690235194</v>
       </c>
       <c r="C3" t="n">
-        <v>14.29424657383356</v>
+        <v>17.27875959474386</v>
       </c>
       <c r="D3" t="n">
-        <v>52.327152636355</v>
+        <v>54.52626749386786</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.69808903764427</v>
+        <v>32.48112279500572</v>
       </c>
       <c r="C4" t="n">
-        <v>44.27387621841841</v>
+        <v>64.57936398535519</v>
       </c>
       <c r="D4" t="n">
-        <v>137.0843771870949</v>
+        <v>139.3178532142564</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.52474596681587</v>
+        <v>58.88031856220246</v>
       </c>
       <c r="C5" t="n">
-        <v>124.2156282798277</v>
+        <v>181.5251505152353</v>
       </c>
       <c r="D5" t="n">
-        <v>152.4899621621358</v>
+        <v>159.9757884070178</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.70328518026855</v>
+        <v>63.07434475474484</v>
       </c>
       <c r="C6" t="n">
-        <v>267.9552731540118</v>
+        <v>324.7906112482681</v>
       </c>
       <c r="D6" t="n">
-        <v>95.79894098040377</v>
+        <v>102.7624774466264</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.36924461445059</v>
+        <v>31.91956310817654</v>
       </c>
       <c r="C7" t="n">
-        <v>336.8621810196868</v>
+        <v>363.2122894016712</v>
       </c>
       <c r="D7" t="n">
-        <v>51.26293812495145</v>
+        <v>53.53862930339555</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>250.1787674732147</v>
+        <v>274.2953998280375</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>114.3765527878661</v>
+        <v>131.571863827749</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>46.40721397974673</v>
+        <v>48.82722207071512</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.165956419746716</v>
+        <v>6.844744994008762</v>
       </c>
       <c r="C2" t="n">
-        <v>2.521128104505809</v>
+        <v>9.209775213539329</v>
       </c>
       <c r="D2" t="n">
-        <v>4.779147824273473</v>
+        <v>17.44860194757856</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.390956570468483</v>
+        <v>2.294344384824796</v>
       </c>
       <c r="C2" t="n">
-        <v>2.66544501703009</v>
+        <v>3.791509633801182</v>
       </c>
       <c r="D2" t="n">
-        <v>8.847510310672256</v>
+        <v>7.495643721924397</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.10557108816893</v>
+        <v>14.74585051778709</v>
       </c>
       <c r="C3" t="n">
-        <v>17.92180434102552</v>
+        <v>22.10404956111694</v>
       </c>
       <c r="D3" t="n">
-        <v>57.11317269455819</v>
+        <v>58.76250883769284</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.74158903626739</v>
+        <v>44.60570694245383</v>
       </c>
       <c r="C4" t="n">
-        <v>65.74077151947917</v>
+        <v>96.67760517570466</v>
       </c>
       <c r="D4" t="n">
-        <v>141.9724990065397</v>
+        <v>144.3463649554085</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.37437433715008</v>
+        <v>36.61918936840603</v>
       </c>
       <c r="C5" t="n">
-        <v>208.3514065337794</v>
+        <v>272.2140946950344</v>
       </c>
       <c r="D5" t="n">
-        <v>139.8745041625643</v>
+        <v>146.4767574736241</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.18495378349268</v>
+        <v>19.80381469006666</v>
       </c>
       <c r="C6" t="n">
-        <v>279.6282533575063</v>
+        <v>299.7138296386918</v>
       </c>
       <c r="D6" t="n">
-        <v>75.95487463446298</v>
+        <v>80.02029187774903</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>175.9468600597048</v>
+        <v>192.8947706781175</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>84.28304040958866</v>
+        <v>96.96722074845746</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>24.11663235482289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>35.38905949498476</v>
+        <v>37.27499683484289</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.06125357275758</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.41424077792992</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.49921085984289</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.71908128786517</v>
+        <v>6.816274310585604</v>
       </c>
       <c r="C2" t="n">
-        <v>2.977640786980576</v>
+        <v>4.660356352059609</v>
       </c>
       <c r="D2" t="n">
-        <v>6.490334072775664</v>
+        <v>17.28661357637784</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.97593933347934</v>
+        <v>14.53477476137403</v>
       </c>
       <c r="C3" t="n">
-        <v>6.450082416901544</v>
+        <v>23.2085157283946</v>
       </c>
       <c r="D3" t="n">
-        <v>7.304202919596269</v>
+        <v>17.79417713947344</v>
       </c>
     </row>
     <row r="4">
@@ -4543,10 +4543,10 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
-        <v>19.73116535995239</v>
+        <v>19.62906359871073</v>
       </c>
     </row>
     <row r="5">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39986597192855</v>
+        <v>13.39625428971645</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1522395000965</v>
+        <v>70.13333128145673</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576454820226888</v>
+        <v>1.57602991643723</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.471860792844222</v>
+        <v>4.985314842165304</v>
       </c>
       <c r="C2" t="n">
-        <v>3.597123588360313</v>
+        <v>8.51666133434108</v>
       </c>
       <c r="D2" t="n">
-        <v>12.46525060082175</v>
+        <v>27.75597109446582</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.46176557836127</v>
+        <v>19.96874830438012</v>
       </c>
       <c r="C3" t="n">
-        <v>9.734028487607127</v>
+        <v>20.05710559776234</v>
       </c>
       <c r="D3" t="n">
-        <v>10.99066554904304</v>
+        <v>28.01417074068273</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.06902543893354</v>
+        <v>16.84679060487526</v>
       </c>
       <c r="C4" t="n">
-        <v>10.52924412804704</v>
+        <v>35.91429451675682</v>
       </c>
       <c r="D4" t="n">
-        <v>18.97816487079509</v>
+        <v>24.38955821660351</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.15790681613028</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.42267559664065</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>25.70215489718149</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.53898915629405</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>48.6887956444163</v>
+        <v>47.97801030654161</v>
       </c>
     </row>
     <row r="12">
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44860817235758</v>
+        <v>15.43636525253695</v>
       </c>
       <c r="C21" t="n">
-        <v>86.18697190894231</v>
+        <v>86.11866930362723</v>
       </c>
       <c r="D21" t="n">
-        <v>3.252338562601597</v>
+        <v>3.249761105797254</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.592615760466579</v>
+        <v>6.346998907955629</v>
       </c>
       <c r="C2" t="n">
-        <v>5.274930414918113</v>
+        <v>8.484263660100934</v>
       </c>
       <c r="D2" t="n">
-        <v>13.41460063082842</v>
+        <v>29.3493476184584</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.80752069670539</v>
+        <v>18.61393647251952</v>
       </c>
       <c r="C3" t="n">
-        <v>12.37002107350981</v>
+        <v>27.84236489243954</v>
       </c>
       <c r="D3" t="n">
-        <v>18.41267819314893</v>
+        <v>43.71722527011047</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.22738991895354</v>
+        <v>28.83098483061608</v>
       </c>
       <c r="C4" t="n">
-        <v>18.81224950877738</v>
+        <v>44.19729989748716</v>
       </c>
       <c r="D4" t="n">
-        <v>20.05023336383261</v>
+        <v>32.94058072059322</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.75642875835556</v>
+        <v>14.5298660228528</v>
       </c>
       <c r="C5" t="n">
-        <v>13.54811831860599</v>
+        <v>39.51534509593412</v>
       </c>
       <c r="D5" t="n">
-        <v>29.67332436085985</v>
+        <v>31.41592653589794</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.03524510636165</v>
+        <v>12.31700669748049</v>
       </c>
       <c r="D6" t="n">
-        <v>36.66925850132262</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.43373686329462</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.37389131106456</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.95312245657017</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>50.11036632016568</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.75296528666405</v>
+        <v>16.72370708229238</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1930882486507</v>
+        <v>102.0146132019835</v>
       </c>
       <c r="D21" t="n">
-        <v>5.025889585999216</v>
+        <v>4.180926770573095</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.709844647899449</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C2" t="n">
-        <v>11.43539725906685</v>
+        <v>9.382562809486767</v>
       </c>
       <c r="D2" t="n">
-        <v>22.66070050942488</v>
+        <v>28.75735375279757</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.26265072084841</v>
+        <v>20.238728923048</v>
       </c>
       <c r="C3" t="n">
-        <v>17.22476347101029</v>
+        <v>30.68943323475529</v>
       </c>
       <c r="D3" t="n">
-        <v>24.87257808709294</v>
+        <v>56.29832210003335</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.71161252132547</v>
+        <v>32.71085175779947</v>
       </c>
       <c r="C4" t="n">
-        <v>25.84450831429728</v>
+        <v>58.15971574728529</v>
       </c>
       <c r="D4" t="n">
-        <v>24.77243982125977</v>
+        <v>46.66050488744241</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.1635763181775</v>
+        <v>28.42159603794517</v>
       </c>
       <c r="C5" t="n">
-        <v>25.42726553999239</v>
+        <v>61.43286259324417</v>
       </c>
       <c r="D5" t="n">
-        <v>30.38509144643879</v>
+        <v>35.66198535676539</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.06920536538279</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="C6" t="n">
-        <v>17.02645043475243</v>
+        <v>38.35982804803563</v>
       </c>
       <c r="D6" t="n">
-        <v>37.83655652167208</v>
+        <v>38.60133798328035</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.61249706092553</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>49.11192890494669</v>
+        <v>48.54251523648354</v>
       </c>
     </row>
     <row r="11">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.43390109421063</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.09706684970056</v>
+        <v>18.03931774841122</v>
       </c>
       <c r="C21" t="n">
-        <v>118.0618170670941</v>
+        <v>117.6850729301113</v>
       </c>
       <c r="D21" t="n">
-        <v>6.894120704647832</v>
+        <v>6.013105916137074</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.621888265144736</v>
+        <v>6.410812508731672</v>
       </c>
       <c r="C2" t="n">
-        <v>12.64785567381166</v>
+        <v>7.821583959734339</v>
       </c>
       <c r="D2" t="n">
-        <v>31.18423407769568</v>
+        <v>23.42744546644164</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.35100801423063</v>
+        <v>20.02765316663493</v>
       </c>
       <c r="C3" t="n">
-        <v>31.4404702285041</v>
+        <v>31.82335183316036</v>
       </c>
       <c r="D3" t="n">
-        <v>35.06802799569606</v>
+        <v>61.74702185860314</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.62830283518473</v>
+        <v>26.09976271740145</v>
       </c>
       <c r="C4" t="n">
-        <v>30.09449412598173</v>
+        <v>57.16422357517902</v>
       </c>
       <c r="D4" t="n">
-        <v>27.6568145763369</v>
+        <v>55.35191731313942</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.91751749731004</v>
+        <v>23.75829444277282</v>
       </c>
       <c r="C5" t="n">
-        <v>28.00435326364027</v>
+        <v>63.12637738306992</v>
       </c>
       <c r="D5" t="n">
-        <v>26.18812001078367</v>
+        <v>35.56381058634071</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.96103319146639</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="C6" t="n">
-        <v>20.16607959293373</v>
+        <v>46.57116584635595</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>31.47679489356124</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>14.85187926984575</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>31.32069700858599</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>22.40937309713768</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>30.28593492830985</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.48354395430394</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.080817294394743</v>
+        <v>7.045506356959865</v>
       </c>
       <c r="C21" t="n">
-        <v>67.26776429675006</v>
+        <v>66.05162209649873</v>
       </c>
       <c r="D21" t="n">
-        <v>5.310612970796057</v>
+        <v>4.403441473099916</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.023603002630929</v>
+        <v>5.336780520285661</v>
       </c>
       <c r="C2" t="n">
-        <v>6.773077411598745</v>
+        <v>4.400193210434204</v>
       </c>
       <c r="D2" t="n">
-        <v>28.7642259867273</v>
+        <v>18.64535239905542</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.83268628411732</v>
+        <v>21.52481841561132</v>
       </c>
       <c r="C3" t="n">
-        <v>43.9528447191297</v>
+        <v>31.00359250011427</v>
       </c>
       <c r="D3" t="n">
-        <v>53.6966906837793</v>
+        <v>66.50358948567894</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.97137475232337</v>
+        <v>34.17856457564846</v>
       </c>
       <c r="C4" t="n">
-        <v>61.40144666670826</v>
+        <v>71.1904530257532</v>
       </c>
       <c r="D4" t="n">
-        <v>40.2280939292173</v>
+        <v>74.86611643045326</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.550605897829</v>
+        <v>32.79037332184348</v>
       </c>
       <c r="C5" t="n">
-        <v>45.74944301790137</v>
+        <v>88.74999246391167</v>
       </c>
       <c r="D5" t="n">
-        <v>30.58144098728815</v>
+        <v>47.73748211900116</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.0239471599962</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="C6" t="n">
-        <v>35.22019888985433</v>
+        <v>77.68569583705012</v>
       </c>
       <c r="D6" t="n">
-        <v>32.48308629041422</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.37845589222053</v>
+        <v>11.79766216193392</v>
       </c>
       <c r="C7" t="n">
-        <v>23.71509754378595</v>
+        <v>48.74770050667112</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>19.69385894719101</v>
+        <v>26.78698611037422</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.312168003800915</v>
+        <v>7.262111631353228</v>
       </c>
       <c r="C21" t="n">
-        <v>77.69178504038472</v>
+        <v>75.34440817528976</v>
       </c>
       <c r="D21" t="n">
-        <v>6.3981470033258</v>
+        <v>5.446583723514921</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.532729150507524</v>
+        <v>4.248022316275948</v>
       </c>
       <c r="C2" t="n">
-        <v>4.393320976504477</v>
+        <v>12.12949288596934</v>
       </c>
       <c r="D2" t="n">
-        <v>23.65030219530566</v>
+        <v>15.06099153085032</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.94282195344221</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="C3" t="n">
-        <v>32.98181412417159</v>
+        <v>22.83054286225958</v>
       </c>
       <c r="D3" t="n">
-        <v>64.88370577367169</v>
+        <v>65.88017969348221</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.11849803924015</v>
+        <v>38.60722846950582</v>
       </c>
       <c r="C4" t="n">
-        <v>91.08753374772331</v>
+        <v>74.176929542072</v>
       </c>
       <c r="D4" t="n">
-        <v>59.04034343799469</v>
+        <v>89.74744813142641</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.45367491701582</v>
+        <v>42.41150082346221</v>
       </c>
       <c r="C5" t="n">
-        <v>85.75566196595889</v>
+        <v>112.7782675253524</v>
       </c>
       <c r="D5" t="n">
-        <v>38.63177216211199</v>
+        <v>63.83814446864886</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.96610616090365</v>
+        <v>34.93843729873549</v>
       </c>
       <c r="C6" t="n">
-        <v>56.23156325614456</v>
+        <v>111.9801066417997</v>
       </c>
       <c r="D6" t="n">
-        <v>34.89818564286137</v>
+        <v>42.54600025894403</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>39.40538935305847</v>
+        <v>82.28420208374216</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>26.70353755551324</v>
+        <v>47.31533060617502</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>24.84999788989526</v>
+        <v>29.17656002251095</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.61656292046278</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.12466626290612</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.531170239763797</v>
+        <v>7.465323318260624</v>
       </c>
       <c r="C21" t="n">
-        <v>87.54985403725414</v>
+        <v>83.98488733043202</v>
       </c>
       <c r="D21" t="n">
-        <v>7.531170239763797</v>
+        <v>6.532157903478045</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_83_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626916771</v>
+        <v>10.84497641139834</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907172222246</v>
+        <v>37.78907221782182</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.232134426558751</v>
+        <v>5.768749510154257</v>
       </c>
       <c r="C2" t="n">
-        <v>7.134360566761572</v>
+        <v>11.62389281828223</v>
       </c>
       <c r="D2" t="n">
-        <v>22.72451411020092</v>
+        <v>36.98243601897735</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.91060420565131</v>
+        <v>19.86075605691298</v>
       </c>
       <c r="C3" t="n">
-        <v>36.01541453029424</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D3" t="n">
-        <v>62.70422587024377</v>
+        <v>82.57479940419923</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.02014334236623</v>
+        <v>44.72057142385071</v>
       </c>
       <c r="C4" t="n">
-        <v>65.08987279156354</v>
+        <v>86.04625928641595</v>
       </c>
       <c r="D4" t="n">
-        <v>101.106269069562</v>
+        <v>102.3187274843068</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.31456984264904</v>
+        <v>55.39511421212629</v>
       </c>
       <c r="C5" t="n">
-        <v>123.970191353766</v>
+        <v>115.895316486336</v>
       </c>
       <c r="D5" t="n">
-        <v>79.03069019186825</v>
+        <v>71.91301933607888</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.68562941712533</v>
+        <v>46.77242412572655</v>
       </c>
       <c r="C6" t="n">
-        <v>145.831749231934</v>
+        <v>108.8002258277443</v>
       </c>
       <c r="D6" t="n">
-        <v>52.08564270111029</v>
+        <v>47.45670227558657</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.9014907388726</v>
+        <v>31.26081039862693</v>
       </c>
       <c r="C7" t="n">
-        <v>121.0907253372101</v>
+        <v>88.75195595932016</v>
       </c>
       <c r="D7" t="n">
-        <v>40.3036885024443</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.52143120414207</v>
+        <v>15.68832831386403</v>
       </c>
       <c r="C8" t="n">
-        <v>78.27474445959818</v>
+        <v>53.7408693304704</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>43.93124626963626</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.65394637898884</v>
+        <v>7.689556694093992</v>
       </c>
       <c r="C21" t="n">
-        <v>92.80409984523968</v>
+        <v>94.19706950265139</v>
       </c>
       <c r="D21" t="n">
-        <v>7.65394637898884</v>
+        <v>8.65075128085574</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.655668597716628</v>
+        <v>7.065638227464294</v>
       </c>
       <c r="C2" t="n">
-        <v>8.93488585635022</v>
+        <v>15.68440132304704</v>
       </c>
       <c r="D2" t="n">
-        <v>29.70768553050848</v>
+        <v>37.11889894986766</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.61393647251952</v>
+        <v>19.44351328260808</v>
       </c>
       <c r="C3" t="n">
-        <v>31.67608967752334</v>
+        <v>37.20332925243288</v>
       </c>
       <c r="D3" t="n">
-        <v>65.10459900712723</v>
+        <v>90.93928984438205</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.74012426247764</v>
+        <v>40.89175537728815</v>
       </c>
       <c r="C4" t="n">
-        <v>76.257252927371</v>
+        <v>78.97571232043042</v>
       </c>
       <c r="D4" t="n">
-        <v>106.5687132959913</v>
+        <v>117.5446526294706</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.11255079975246</v>
+        <v>61.04016351154545</v>
       </c>
       <c r="C5" t="n">
-        <v>121.9330648674539</v>
+        <v>136.3156687346697</v>
       </c>
       <c r="D5" t="n">
-        <v>94.34595437811849</v>
+        <v>88.21003122657592</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.94980166502573</v>
+        <v>59.08943082320704</v>
       </c>
       <c r="C6" t="n">
-        <v>167.8494049950772</v>
+        <v>142.5713651061303</v>
       </c>
       <c r="D6" t="n">
-        <v>62.02780170201773</v>
+        <v>57.64037121173875</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.14210104187108</v>
+        <v>42.22006002113408</v>
       </c>
       <c r="C7" t="n">
-        <v>162.3525995989993</v>
+        <v>120.9110655073329</v>
       </c>
       <c r="D7" t="n">
-        <v>45.33416373900496</v>
+        <v>43.47767883027424</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.36559536107409</v>
+        <v>24.03318379996192</v>
       </c>
       <c r="C8" t="n">
-        <v>114.658314378985</v>
+        <v>82.6140693123691</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.20468654856884</v>
+        <v>11.31562403914873</v>
       </c>
       <c r="C9" t="n">
-        <v>67.56093176315272</v>
+        <v>48.36874589283183</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.826688126649962</v>
+        <v>7.866768825984126</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7686096306183</v>
+        <v>102.2679947377936</v>
       </c>
       <c r="D21" t="n">
-        <v>8.805024142481209</v>
+        <v>9.833461032480157</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.910923000820798</v>
+        <v>9.968666188922112</v>
       </c>
       <c r="C2" t="n">
-        <v>14.83028082035232</v>
+        <v>16.41776685811941</v>
       </c>
       <c r="D2" t="n">
-        <v>28.75048151886784</v>
+        <v>43.09774246873073</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.47573103039898</v>
+        <v>20.89159114637213</v>
       </c>
       <c r="C3" t="n">
-        <v>32.7511034136736</v>
+        <v>47.60494617892783</v>
       </c>
       <c r="D3" t="n">
-        <v>70.94599784739574</v>
+        <v>96.47634689633406</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.07646281440679</v>
+        <v>38.22434686484957</v>
       </c>
       <c r="C4" t="n">
-        <v>77.23998237932204</v>
+        <v>84.06803766235862</v>
       </c>
       <c r="D4" t="n">
-        <v>112.3502255263007</v>
+        <v>129.9627793404885</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.30260894374884</v>
+        <v>60.77018289287758</v>
       </c>
       <c r="C5" t="n">
-        <v>128.1671627894211</v>
+        <v>138.5736884544373</v>
       </c>
       <c r="D5" t="n">
-        <v>105.4151597435013</v>
+        <v>105.3660723582889</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.98755004614362</v>
+        <v>68.95108651236625</v>
       </c>
       <c r="C6" t="n">
-        <v>177.3890474372435</v>
+        <v>173.9676566879433</v>
       </c>
       <c r="D6" t="n">
-        <v>73.05675541152641</v>
+        <v>67.98504677138737</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.2030515149924</v>
+        <v>53.29908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>194.9309154167254</v>
+        <v>155.4057528437488</v>
       </c>
       <c r="D7" t="n">
-        <v>51.26293812495145</v>
+        <v>48.80758711663017</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.79389940203295</v>
+        <v>32.71183350550372</v>
       </c>
       <c r="C8" t="n">
-        <v>157.2170773580842</v>
+        <v>114.574865824124</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.19687362466387</v>
+        <v>16.41874860582365</v>
       </c>
       <c r="C9" t="n">
-        <v>97.62499171030279</v>
+        <v>71.22186895228909</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>56.51430659496764</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>35.00617789032851</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.983208760717872</v>
+        <v>8.026618431767414</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7733182696913</v>
+        <v>110.3660034368019</v>
       </c>
       <c r="D21" t="n">
-        <v>9.97901095089734</v>
+        <v>11.03660034368019</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.324819621385452</v>
+        <v>8.945685081096936</v>
       </c>
       <c r="C2" t="n">
-        <v>10.32111361474672</v>
+        <v>11.42656152972863</v>
       </c>
       <c r="D2" t="n">
-        <v>23.68073637413731</v>
+        <v>35.40378571054848</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.51914891356409</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="C3" t="n">
-        <v>51.69883410563704</v>
+        <v>67.89276248718816</v>
       </c>
       <c r="D3" t="n">
-        <v>77.97531140980291</v>
+        <v>103.3387633490193</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.12979598560561</v>
+        <v>29.18834099496192</v>
       </c>
       <c r="C4" t="n">
-        <v>105.4966448029537</v>
+        <v>114.3667353108237</v>
       </c>
       <c r="D4" t="n">
-        <v>111.2271061526424</v>
+        <v>122.7007915721749</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.90113088597411</v>
+        <v>38.82812170296135</v>
       </c>
       <c r="C5" t="n">
-        <v>105.9796646734432</v>
+        <v>103.9425381871311</v>
       </c>
       <c r="D5" t="n">
-        <v>71.98665041389738</v>
+        <v>68.94323253073227</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.79880814055419</v>
+        <v>33.08686112852601</v>
       </c>
       <c r="C6" t="n">
-        <v>128.3625305825663</v>
+        <v>102.3599608878852</v>
       </c>
       <c r="D6" t="n">
-        <v>33.73088762251191</v>
+        <v>32.12082138754715</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.67895280517807</v>
       </c>
       <c r="C7" t="n">
-        <v>110.5506819844163</v>
+        <v>80.54749039492954</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>28.38625312059227</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>11.34900346109313</v>
       </c>
       <c r="C8" t="n">
-        <v>71.9326542901638</v>
+        <v>52.48914100755572</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>43.15468383557703</v>
+        <v>32.9484347022272</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.478733026773948</v>
+        <v>5.322054304721958</v>
       </c>
       <c r="C2" t="n">
-        <v>4.76442160870977</v>
+        <v>4.927391727614741</v>
       </c>
       <c r="D2" t="n">
-        <v>16.60528066963055</v>
+        <v>24.34439782220816</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.42235680147115</v>
+        <v>28.51977080836984</v>
       </c>
       <c r="C3" t="n">
-        <v>46.94226647856124</v>
+        <v>57.39297079026854</v>
       </c>
       <c r="D3" t="n">
-        <v>79.72773106188347</v>
+        <v>108.3947640258903</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.19132729580366</v>
+        <v>37.54792269662352</v>
       </c>
       <c r="C4" t="n">
-        <v>119.3824843318206</v>
+        <v>143.3253473429918</v>
       </c>
       <c r="D4" t="n">
-        <v>122.0881810047248</v>
+        <v>141.1684476367616</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.23907308041327</v>
+        <v>43.04963683122264</v>
       </c>
       <c r="C5" t="n">
-        <v>147.9248353373882</v>
+        <v>153.520797251595</v>
       </c>
       <c r="D5" t="n">
-        <v>89.55993431991529</v>
+        <v>89.65810909033996</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.27303333943441</v>
+        <v>39.24536447726626</v>
       </c>
       <c r="C6" t="n">
-        <v>151.4669810543107</v>
+        <v>131.5021597407475</v>
       </c>
       <c r="D6" t="n">
-        <v>41.57996051796516</v>
+        <v>39.64788103600744</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.70269467652924</v>
+        <v>20.18178755620168</v>
       </c>
       <c r="C7" t="n">
-        <v>139.6555744245173</v>
+        <v>105.1010004781423</v>
       </c>
       <c r="D7" t="n">
         <v>30.9014907388726</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>96.04928664498669</v>
+        <v>69.9298889735003</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>47.03749600587317</v>
+        <v>37.05312185368311</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.64464838879166</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C2" t="n">
-        <v>5.067781649322035</v>
+        <v>3.566689409528662</v>
       </c>
       <c r="D2" t="n">
-        <v>13.13971127363931</v>
+        <v>22.36813969355933</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.51852701875834</v>
+        <v>23.30669049881928</v>
       </c>
       <c r="C3" t="n">
-        <v>32.05897128217959</v>
+        <v>37.95436624618169</v>
       </c>
       <c r="D3" t="n">
-        <v>74.8140838021282</v>
+        <v>102.9215205747144</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.58545009356314</v>
+        <v>45.42252103238718</v>
       </c>
       <c r="C4" t="n">
-        <v>118.1700259170758</v>
+        <v>143.1083811003533</v>
       </c>
       <c r="D4" t="n">
-        <v>132.2728316885812</v>
+        <v>159.8275445036765</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.25227776892498</v>
+        <v>49.01375413452202</v>
       </c>
       <c r="C5" t="n">
-        <v>183.8813450054276</v>
+        <v>205.4061634210389</v>
       </c>
       <c r="D5" t="n">
-        <v>109.121257327033</v>
+        <v>114.8399377042707</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.03531152628644</v>
+        <v>47.17494068446774</v>
       </c>
       <c r="C6" t="n">
-        <v>189.384040887731</v>
+        <v>182.2192461421378</v>
       </c>
       <c r="D6" t="n">
-        <v>56.19131160027045</v>
+        <v>54.58124536530568</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.98511922018283</v>
+        <v>30.12296480940488</v>
       </c>
       <c r="C7" t="n">
-        <v>177.0248190389678</v>
+        <v>144.2069567814055</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>13.93590866178347</v>
       </c>
       <c r="C8" t="n">
-        <v>135.5204530942297</v>
+        <v>100.5555086074795</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2436,7 +2436,7 @@
         <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>76.65780599070366</v>
+        <v>57.57655761096267</v>
       </c>
       <c r="D9" t="n">
         <v>29.28749751309084</v>
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>42.27896488338889</v>
+        <v>36.72718161587318</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2481,7 +2481,7 @@
         <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.797980957103409</v>
+        <v>3.637375244234432</v>
       </c>
       <c r="C2" t="n">
-        <v>2.422953334081128</v>
+        <v>1.727875959474386</v>
       </c>
       <c r="D2" t="n">
-        <v>9.173450548482196</v>
+        <v>15.60193451589031</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.58234061953438</v>
+        <v>23.93991776805847</v>
       </c>
       <c r="C3" t="n">
-        <v>28.92719610563227</v>
+        <v>30.48326621686346</v>
       </c>
       <c r="D3" t="n">
-        <v>72.18790869326797</v>
+        <v>101.5421650502476</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.49084246105696</v>
+        <v>50.06815116888308</v>
       </c>
       <c r="C4" t="n">
-        <v>116.0258889310008</v>
+        <v>140.211243625121</v>
       </c>
       <c r="D4" t="n">
-        <v>140.517548908846</v>
+        <v>173.0880107449382</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.43666641087414</v>
+        <v>50.73181261695394</v>
       </c>
       <c r="C5" t="n">
-        <v>223.2003405605124</v>
+        <v>249.7566159603886</v>
       </c>
       <c r="D5" t="n">
-        <v>114.7172192412398</v>
+        <v>120.80405500757</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.46170882509904</v>
+        <v>36.99127174831558</v>
       </c>
       <c r="C6" t="n">
-        <v>223.7992066601029</v>
+        <v>211.2809416832519</v>
       </c>
       <c r="D6" t="n">
-        <v>54.70200033292804</v>
+        <v>52.72966919509619</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.92310488389926</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>181.2168817361017</v>
+        <v>143.4284308519377</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>96.29963230956963</v>
+        <v>71.01472018669303</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.28280975874785</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2778,7 +2778,7 @@
         <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.363467634749572</v>
+        <v>5.028511741152163</v>
       </c>
       <c r="C2" t="n">
-        <v>4.565126824747668</v>
+        <v>7.936448441131216</v>
       </c>
       <c r="D2" t="n">
-        <v>10.43205110532661</v>
+        <v>16.56895600457342</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.34471661737765</v>
+        <v>18.52067044061608</v>
       </c>
       <c r="C3" t="n">
-        <v>19.18825887950391</v>
+        <v>18.82501222893259</v>
       </c>
       <c r="D3" t="n">
-        <v>64.44682804528188</v>
+        <v>91.86704142489528</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.96382387032566</v>
+        <v>47.77086154094555</v>
       </c>
       <c r="C4" t="n">
-        <v>95.91184196639215</v>
+        <v>111.1377671115559</v>
       </c>
       <c r="D4" t="n">
-        <v>143.4912627050096</v>
+        <v>181.7794231706351</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.10058990085224</v>
+        <v>60.69655181505907</v>
       </c>
       <c r="C5" t="n">
-        <v>218.5124952727339</v>
+        <v>252.9472959991907</v>
       </c>
       <c r="D5" t="n">
-        <v>133.6158625479909</v>
+        <v>148.8084082712103</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.0478943199924</v>
+        <v>48.66425195181016</v>
       </c>
       <c r="C6" t="n">
-        <v>284.8609686211418</v>
+        <v>293.5150746340775</v>
       </c>
       <c r="D6" t="n">
-        <v>72.45298057341462</v>
+        <v>70.19888784446394</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.16371518689774</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>240.8639452553209</v>
+        <v>208.4054026575129</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>153.2115467247572</v>
+        <v>116.4941825859265</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>63.23436963053704</v>
+        <v>48.92343334573128</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3173,7 +3173,7 @@
         <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.276672926148354</v>
+        <v>3.410591524553419</v>
       </c>
       <c r="C2" t="n">
-        <v>4.092906179004952</v>
+        <v>4.197953183359361</v>
       </c>
       <c r="D2" t="n">
-        <v>8.779769719079225</v>
+        <v>12.46819584393449</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.85246010692249</v>
+        <v>17.99543541884404</v>
       </c>
       <c r="C3" t="n">
-        <v>18.71701998146544</v>
+        <v>24.1755372170777</v>
       </c>
       <c r="D3" t="n">
-        <v>59.6657167255999</v>
+        <v>86.00109889202059</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.09671966329748</v>
+        <v>44.04414725562465</v>
       </c>
       <c r="C4" t="n">
-        <v>78.55454255530854</v>
+        <v>88.13934539187015</v>
       </c>
       <c r="D4" t="n">
-        <v>143.5040254251647</v>
+        <v>185.1104931311446</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.22393025868885</v>
+        <v>65.55620295108078</v>
       </c>
       <c r="C5" t="n">
-        <v>208.4741249968102</v>
+        <v>244.2097414313941</v>
       </c>
       <c r="D5" t="n">
-        <v>147.1394371739907</v>
+        <v>168.3206438931157</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.61520562432682</v>
+        <v>56.27181491201868</v>
       </c>
       <c r="C6" t="n">
-        <v>318.7931145230243</v>
+        <v>339.8447305451887</v>
       </c>
       <c r="D6" t="n">
-        <v>84.24671574453156</v>
+        <v>84.08570912103508</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>17.30723027816702</v>
       </c>
       <c r="C7" t="n">
-        <v>300.2714623347039</v>
+        <v>269.7891778655447</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49575119957818</v>
+        <v>44.31609136970101</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>196.2710010330223</v>
+        <v>154.212929383089</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>71.55468142402876</v>
+        <v>52.80624551602742</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
         <v>19.7439280801076</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.06233313145306</v>
+      </c>
+      <c r="D14" t="n">
         <v>10.75504610002381</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3470,7 +3470,7 @@
         <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.171045084717197</v>
+        <v>4.93720920465721</v>
       </c>
       <c r="C2" t="n">
-        <v>6.49131582047991</v>
+        <v>8.699266407330986</v>
       </c>
       <c r="D2" t="n">
-        <v>10.07567668868501</v>
+        <v>18.74254542177585</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.94648690235194</v>
+        <v>14.90783888898781</v>
       </c>
       <c r="C3" t="n">
-        <v>17.27875959474386</v>
+        <v>20.7443289907351</v>
       </c>
       <c r="D3" t="n">
-        <v>54.52626749386786</v>
+        <v>77.98022014832415</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.48112279500572</v>
+        <v>39.0411609547829</v>
       </c>
       <c r="C4" t="n">
-        <v>64.57936398535519</v>
+        <v>76.34659196845746</v>
       </c>
       <c r="D4" t="n">
-        <v>139.3178532142564</v>
+        <v>184.6510352055571</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.88031856220246</v>
+        <v>65.35985341023141</v>
       </c>
       <c r="C5" t="n">
-        <v>181.5251505152353</v>
+        <v>208.7931930006905</v>
       </c>
       <c r="D5" t="n">
-        <v>159.9757884070178</v>
+        <v>186.6056948847125</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.07434475474484</v>
+        <v>67.26051696565324</v>
       </c>
       <c r="C6" t="n">
-        <v>324.7906112482681</v>
+        <v>359.2460286765141</v>
       </c>
       <c r="D6" t="n">
-        <v>102.7624774466264</v>
+        <v>104.2920403698429</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.91956310817654</v>
+        <v>32.39865598784899</v>
       </c>
       <c r="C7" t="n">
-        <v>363.2122894016712</v>
+        <v>355.486916716953</v>
       </c>
       <c r="D7" t="n">
-        <v>53.53862930339555</v>
+        <v>53.35896947351839</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>274.2953998280375</v>
+        <v>225.8117894538088</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>131.571863827749</v>
+        <v>99.51092905016091</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>48.82722207071512</v>
+        <v>40.28601704376787</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.844744994008762</v>
+        <v>5.981788761975816</v>
       </c>
       <c r="C2" t="n">
-        <v>9.209775213539329</v>
+        <v>2.978622534684823</v>
       </c>
       <c r="D2" t="n">
-        <v>17.44860194757856</v>
+        <v>11.41281706186917</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.294344384824796</v>
+        <v>3.6471927212769</v>
       </c>
       <c r="C2" t="n">
-        <v>3.791509633801182</v>
+        <v>5.14926670877452</v>
       </c>
       <c r="D2" t="n">
-        <v>7.495643721924397</v>
+        <v>13.94376264341745</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.74585051778709</v>
+        <v>19.39442589739574</v>
       </c>
       <c r="C3" t="n">
-        <v>22.10404956111694</v>
+        <v>27.93072218582175</v>
       </c>
       <c r="D3" t="n">
-        <v>58.76250883769284</v>
+        <v>85.55931242510952</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.60570694245383</v>
+        <v>51.35718590455915</v>
       </c>
       <c r="C4" t="n">
-        <v>96.67760517570466</v>
+        <v>112.4395645673872</v>
       </c>
       <c r="D4" t="n">
-        <v>144.3463649554085</v>
+        <v>187.2929182776853</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.61918936840603</v>
+        <v>37.89546138392689</v>
       </c>
       <c r="C5" t="n">
-        <v>272.2140946950344</v>
+        <v>308.4405849817417</v>
       </c>
       <c r="D5" t="n">
-        <v>146.4767574736241</v>
+        <v>164.3445656909161</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.80381469006666</v>
+        <v>20.0855762811855</v>
       </c>
       <c r="C6" t="n">
-        <v>299.7138296386918</v>
+        <v>293.9980945045669</v>
       </c>
       <c r="D6" t="n">
-        <v>80.02029187774903</v>
+        <v>80.9863316187279</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>192.8947706781175</v>
+        <v>158.7594030014559</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>31.9794497181356</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>96.96722074845746</v>
+        <v>73.35127972280043</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>19.85781081380023</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.816274310585604</v>
+        <v>6.780931393232719</v>
       </c>
       <c r="C2" t="n">
-        <v>4.660356352059609</v>
+        <v>6.069164307653782</v>
       </c>
       <c r="D2" t="n">
-        <v>17.28661357637784</v>
+        <v>12.56931585747191</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.53477476137403</v>
+        <v>12.70872403147496</v>
       </c>
       <c r="C3" t="n">
-        <v>23.2085157283946</v>
+        <v>7.505461198966866</v>
       </c>
       <c r="D3" t="n">
-        <v>17.79417713947344</v>
+        <v>12.72345024703866</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39625428971645</v>
+        <v>13.39850464483496</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13333128145673</v>
+        <v>70.14511255237124</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57602991643723</v>
+        <v>1.57629466409823</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.985314842165304</v>
+        <v>4.976479112827081</v>
       </c>
       <c r="C2" t="n">
-        <v>8.51666133434108</v>
+        <v>6.608143797285281</v>
       </c>
       <c r="D2" t="n">
-        <v>27.75597109446582</v>
+        <v>22.70193391300324</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.96874830438012</v>
+        <v>19.13426275577033</v>
       </c>
       <c r="C3" t="n">
-        <v>20.05710559776234</v>
+        <v>17.78926840095221</v>
       </c>
       <c r="D3" t="n">
-        <v>28.01417074068273</v>
+        <v>20.20436775339936</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.84679060487526</v>
+        <v>14.77922993973148</v>
       </c>
       <c r="C4" t="n">
-        <v>35.91429451675682</v>
+        <v>12.16287230791373</v>
       </c>
       <c r="D4" t="n">
-        <v>24.38955821660351</v>
+        <v>21.73491242432013</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.42267559664065</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43636525253695</v>
+        <v>15.44368103498713</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11866930362723</v>
+        <v>86.15948366887557</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249761105797254</v>
+        <v>3.251301270523606</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.346998907955629</v>
+        <v>6.857507714163971</v>
       </c>
       <c r="C2" t="n">
-        <v>8.484263660100934</v>
+        <v>5.922883899721008</v>
       </c>
       <c r="D2" t="n">
-        <v>29.3493476184584</v>
+        <v>30.15438073594078</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.61393647251952</v>
+        <v>18.06415775814131</v>
       </c>
       <c r="C3" t="n">
-        <v>27.84236489243954</v>
+        <v>22.59492341324034</v>
       </c>
       <c r="D3" t="n">
-        <v>43.71722527011047</v>
+        <v>33.6739462556656</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.83098483061608</v>
+        <v>27.31222113214627</v>
       </c>
       <c r="C4" t="n">
-        <v>44.19729989748716</v>
+        <v>31.21761349964007</v>
       </c>
       <c r="D4" t="n">
-        <v>32.94058072059322</v>
+        <v>26.98039040811084</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.5298660228528</v>
+        <v>13.13087554430109</v>
       </c>
       <c r="C5" t="n">
-        <v>39.51534509593412</v>
+        <v>15.06982726018854</v>
       </c>
       <c r="D5" t="n">
-        <v>31.41592653589794</v>
+        <v>30.23782929080177</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.31700669748049</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72370708229238</v>
+        <v>16.74024873951915</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0146132019835</v>
+        <v>102.1155173110668</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180926770573095</v>
+        <v>5.022074621855745</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.159886007071988</v>
+        <v>7.051893759604838</v>
       </c>
       <c r="C2" t="n">
-        <v>9.382562809486767</v>
+        <v>6.585563600087604</v>
       </c>
       <c r="D2" t="n">
-        <v>28.75735375279757</v>
+        <v>28.37349040043707</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.238728923048</v>
+        <v>21.04867077905162</v>
       </c>
       <c r="C3" t="n">
-        <v>30.68943323475529</v>
+        <v>22.81090790817464</v>
       </c>
       <c r="D3" t="n">
-        <v>56.29832210003335</v>
+        <v>49.10211142790422</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.71085175779947</v>
+        <v>31.60049510429634</v>
       </c>
       <c r="C4" t="n">
-        <v>58.15971574728529</v>
+        <v>45.06516486804134</v>
       </c>
       <c r="D4" t="n">
-        <v>46.66050488744241</v>
+        <v>36.94807484932871</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.42159603794517</v>
+        <v>26.92443078896878</v>
       </c>
       <c r="C5" t="n">
-        <v>61.43286259324417</v>
+        <v>38.48451000647497</v>
       </c>
       <c r="D5" t="n">
-        <v>35.66198535676539</v>
+        <v>33.25670348136071</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.59876828859932</v>
+        <v>11.83398682699105</v>
       </c>
       <c r="C6" t="n">
+        <v>18.39500673447249</v>
+      </c>
+      <c r="D6" t="n">
         <v>38.35982804803563</v>
-      </c>
-      <c r="D6" t="n">
-        <v>38.60133798328035</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03931774841122</v>
+        <v>18.06913587882952</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6850729301113</v>
+        <v>117.8796007333164</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013105916137074</v>
+        <v>6.8834803347922</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.410812508731672</v>
+        <v>8.556912990215199</v>
       </c>
       <c r="C2" t="n">
-        <v>7.821583959734339</v>
+        <v>12.53986342634451</v>
       </c>
       <c r="D2" t="n">
-        <v>23.42744546644164</v>
+        <v>32.37509404294707</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.02765316663493</v>
+        <v>20.57252314249191</v>
       </c>
       <c r="C3" t="n">
-        <v>31.82335183316036</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D3" t="n">
-        <v>61.74702185860314</v>
+        <v>56.2050560681299</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.09976271740145</v>
+        <v>26.57198336314417</v>
       </c>
       <c r="C4" t="n">
-        <v>57.16422357517902</v>
+        <v>42.99760420289756</v>
       </c>
       <c r="D4" t="n">
-        <v>55.35191731313942</v>
+        <v>45.40975831223197</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.75829444277282</v>
+        <v>22.82563412373834</v>
       </c>
       <c r="C5" t="n">
-        <v>63.12637738306992</v>
+        <v>46.80482179996669</v>
       </c>
       <c r="D5" t="n">
-        <v>35.56381058634071</v>
+        <v>31.73499453977815</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.68556299720054</v>
+        <v>13.36354975020759</v>
       </c>
       <c r="C6" t="n">
-        <v>46.57116584635595</v>
+        <v>27.45162930614931</v>
       </c>
       <c r="D6" t="n">
-        <v>31.47679489356124</v>
+        <v>31.27553661419064</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>15.51063197939536</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
         <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.045506356959865</v>
+        <v>7.06335741083136</v>
       </c>
       <c r="C21" t="n">
-        <v>66.05162209649873</v>
+        <v>66.218975726544</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403441473099916</v>
+        <v>5.29751805812352</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.336780520285661</v>
+        <v>6.175193059712438</v>
       </c>
       <c r="C2" t="n">
-        <v>4.400193210434204</v>
+        <v>8.856346040010477</v>
       </c>
       <c r="D2" t="n">
-        <v>18.64535239905542</v>
+        <v>32.54297290037327</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.52481841561132</v>
+        <v>26.37465207459056</v>
       </c>
       <c r="C3" t="n">
-        <v>31.00359250011427</v>
+        <v>39.74114706791089</v>
       </c>
       <c r="D3" t="n">
-        <v>66.50358948567894</v>
+        <v>69.81698798751192</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.17856457564846</v>
+        <v>35.23787034853076</v>
       </c>
       <c r="C4" t="n">
-        <v>71.1904530257532</v>
+        <v>51.71454206890498</v>
       </c>
       <c r="D4" t="n">
-        <v>74.86611643045326</v>
+        <v>63.89017709697393</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.79037332184348</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="C5" t="n">
-        <v>88.74999246391167</v>
+        <v>67.17608666308801</v>
       </c>
       <c r="D5" t="n">
-        <v>47.73748211900116</v>
+        <v>41.96971435655115</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.94973524510094</v>
+        <v>23.70822530985623</v>
       </c>
       <c r="C6" t="n">
-        <v>77.68569583705012</v>
+        <v>55.50703345041042</v>
       </c>
       <c r="D6" t="n">
-        <v>36.14598697495907</v>
+        <v>34.49566908412018</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.79766216193392</v>
+        <v>11.61800233205675</v>
       </c>
       <c r="C7" t="n">
-        <v>48.74770050667112</v>
+        <v>29.88341836956866</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>26.78698611037422</v>
+        <v>20.27799883121787</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.262111631353228</v>
+        <v>7.286283621340009</v>
       </c>
       <c r="C21" t="n">
-        <v>75.34440817528976</v>
+        <v>75.59519257140259</v>
       </c>
       <c r="D21" t="n">
-        <v>5.446583723514921</v>
+        <v>6.375498168672507</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.248022316275948</v>
+        <v>4.901866287304324</v>
       </c>
       <c r="C2" t="n">
-        <v>12.12949288596934</v>
+        <v>6.169302573486956</v>
       </c>
       <c r="D2" t="n">
-        <v>15.06099153085032</v>
+        <v>27.60576369571606</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.78221624057323</v>
+        <v>23.56194490192345</v>
       </c>
       <c r="C3" t="n">
-        <v>22.83054286225958</v>
+        <v>36.54064955206628</v>
       </c>
       <c r="D3" t="n">
-        <v>65.88017969348221</v>
+        <v>79.64919124554373</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.60722846950582</v>
+        <v>44.52913062152258</v>
       </c>
       <c r="C4" t="n">
-        <v>74.176929542072</v>
+        <v>79.86910273129502</v>
       </c>
       <c r="D4" t="n">
-        <v>89.74744813142641</v>
+        <v>84.52749558794612</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.41150082346221</v>
+        <v>43.46687960552754</v>
       </c>
       <c r="C5" t="n">
-        <v>112.7782675253524</v>
+        <v>83.42401116837273</v>
       </c>
       <c r="D5" t="n">
-        <v>63.83814446864886</v>
+        <v>55.02695882303374</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.93843729873549</v>
+        <v>35.05919226635785</v>
       </c>
       <c r="C6" t="n">
-        <v>111.9801066417997</v>
+        <v>83.723444218168</v>
       </c>
       <c r="D6" t="n">
-        <v>42.54600025894403</v>
+        <v>40.25165587411923</v>
       </c>
     </row>
     <row r="7">
@@ -6451,10 +6451,10 @@
         <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>82.28420208374216</v>
+        <v>56.89227946110266</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>47.31533060617502</v>
+        <v>31.12631096314512</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.17656002251095</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.465323318260624</v>
+        <v>7.495439101252038</v>
       </c>
       <c r="C21" t="n">
-        <v>83.98488733043202</v>
+        <v>85.26061977674193</v>
       </c>
       <c r="D21" t="n">
-        <v>6.532157903478045</v>
+        <v>7.495439101252038</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_83_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641139834</v>
+        <v>10.84497641872106</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907221782182</v>
+        <v>37.78907224333767</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.768749510154257</v>
+        <v>0.6636614480708438</v>
       </c>
       <c r="C2" t="n">
-        <v>11.62389281828223</v>
+        <v>4.763439861005524</v>
       </c>
       <c r="D2" t="n">
-        <v>36.98243601897735</v>
+        <v>20.44096895012284</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.86075605691298</v>
+        <v>5.988660995905544</v>
       </c>
       <c r="C3" t="n">
-        <v>29.45733986592554</v>
+        <v>52.11607687994194</v>
       </c>
       <c r="D3" t="n">
-        <v>82.57479940419923</v>
+        <v>84.31740157923731</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.72057142385071</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C4" t="n">
-        <v>86.04625928641595</v>
+        <v>141.3088375584689</v>
       </c>
       <c r="D4" t="n">
-        <v>102.3187274843068</v>
+        <v>86.32703912983054</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.39511421212629</v>
+        <v>11.65825398793088</v>
       </c>
       <c r="C5" t="n">
-        <v>115.895316486336</v>
+        <v>162.6265072084842</v>
       </c>
       <c r="D5" t="n">
-        <v>71.91301933607888</v>
+        <v>50.020045531375</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.77242412572655</v>
+        <v>8.613854357061516</v>
       </c>
       <c r="C6" t="n">
-        <v>108.8002258277443</v>
+        <v>103.4467555964864</v>
       </c>
       <c r="D6" t="n">
-        <v>47.45670227558657</v>
+        <v>29.26295382048468</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.26081039862693</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>88.75195595932016</v>
+        <v>50.783845245279</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.68832831386403</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>53.7408693304704</v>
+        <v>29.95803119509142</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>32.39374724932775</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.689556694093992</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.19706950265139</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.65075128085574</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.065638227464294</v>
+        <v>0.5939573610693203</v>
       </c>
       <c r="C2" t="n">
-        <v>15.68440132304704</v>
+        <v>10.05407823919158</v>
       </c>
       <c r="D2" t="n">
-        <v>37.11889894986766</v>
+        <v>16.69560145842126</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.44351328260808</v>
+        <v>4.049709280018093</v>
       </c>
       <c r="C3" t="n">
-        <v>37.20332925243288</v>
+        <v>33.49232293037993</v>
       </c>
       <c r="D3" t="n">
-        <v>90.93928984438205</v>
+        <v>81.0874516322653</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.89175537728815</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="C4" t="n">
-        <v>78.97571232043042</v>
+        <v>135.3486472459865</v>
       </c>
       <c r="D4" t="n">
-        <v>117.5446526294706</v>
+        <v>106.6580523370777</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.04016351154545</v>
+        <v>14.23534171157875</v>
       </c>
       <c r="C5" t="n">
-        <v>136.3156687346697</v>
+        <v>215.2727278487194</v>
       </c>
       <c r="D5" t="n">
-        <v>88.21003122657592</v>
+        <v>67.42152358914971</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.08943082320704</v>
+        <v>11.95474179461341</v>
       </c>
       <c r="C6" t="n">
-        <v>142.5713651061303</v>
+        <v>180.1664116925577</v>
       </c>
       <c r="D6" t="n">
-        <v>57.64037121173875</v>
+        <v>36.95102009244145</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.22006002113408</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>120.9110655073329</v>
+        <v>97.73494745317846</v>
       </c>
       <c r="D7" t="n">
-        <v>43.47767883027424</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.03318379996192</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>82.6140693123691</v>
+        <v>47.398779161036</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.31562403914873</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>48.36874589283183</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.9631198600619</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>44.53403936004381</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.866768825984126</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2679947377936</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.833461032480157</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.968666188922112</v>
+        <v>0.3298672286269283</v>
       </c>
       <c r="C2" t="n">
-        <v>16.41776685811941</v>
+        <v>4.466952054322987</v>
       </c>
       <c r="D2" t="n">
-        <v>43.09774246873073</v>
+        <v>11.51491882311084</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.89159114637213</v>
+        <v>3.632466505713198</v>
       </c>
       <c r="C3" t="n">
-        <v>47.60494617892783</v>
+        <v>38.35197406640165</v>
       </c>
       <c r="D3" t="n">
-        <v>96.47634689633406</v>
+        <v>79.40866305800326</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.22434686484957</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C4" t="n">
-        <v>84.06803766235862</v>
+        <v>128.3802020412427</v>
       </c>
       <c r="D4" t="n">
-        <v>129.9627793404885</v>
+        <v>118.5273820814217</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.77018289287758</v>
+        <v>14.40714755982195</v>
       </c>
       <c r="C5" t="n">
-        <v>138.5736884544373</v>
+        <v>255.8189080341127</v>
       </c>
       <c r="D5" t="n">
-        <v>105.3660723582889</v>
+        <v>74.7846313710008</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.95108651236625</v>
+        <v>9.740900721536855</v>
       </c>
       <c r="C6" t="n">
-        <v>173.9676566879433</v>
+        <v>217.6809549672368</v>
       </c>
       <c r="D6" t="n">
-        <v>67.98504677138737</v>
+        <v>37.47429161880501</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.29908286355933</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>155.4057528437488</v>
+        <v>89.35082205891071</v>
       </c>
       <c r="D7" t="n">
-        <v>48.80758711663017</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.71183350550372</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>114.574865824124</v>
+        <v>40.88979188187965</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.41874860582365</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>71.22186895228909</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>43.2754388031994</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.00617789032851</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>38.52377991464484</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.026618431767414</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.3660034368019</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.03660034368019</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.945685081096936</v>
+        <v>0.5861033794353457</v>
       </c>
       <c r="C2" t="n">
-        <v>11.42656152972863</v>
+        <v>11.93216159741573</v>
       </c>
       <c r="D2" t="n">
-        <v>35.40378571054848</v>
+        <v>10.91801621892878</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.5156228333746</v>
+        <v>2.390555659840983</v>
       </c>
       <c r="C3" t="n">
-        <v>67.89276248718816</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D3" t="n">
-        <v>103.3387633490193</v>
+        <v>71.55959016255001</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.18834099496192</v>
+        <v>9.980447161373075</v>
       </c>
       <c r="C4" t="n">
-        <v>114.3667353108237</v>
+        <v>112.8990224929747</v>
       </c>
       <c r="D4" t="n">
-        <v>122.7007915721749</v>
+        <v>129.2735924521073</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.82812170296135</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C5" t="n">
-        <v>103.9425381871311</v>
+        <v>248.8239556413541</v>
       </c>
       <c r="D5" t="n">
-        <v>68.94323253073227</v>
+        <v>96.01492547533807</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.08686112852601</v>
+        <v>13.64531134132642</v>
       </c>
       <c r="C6" t="n">
-        <v>102.3599608878852</v>
+        <v>304.9465449023273</v>
       </c>
       <c r="D6" t="n">
-        <v>32.12082138754715</v>
+        <v>49.59004003691489</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.67895280517807</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>80.54749039492954</v>
+        <v>187.5648623917616</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>35.15344004596554</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>52.48914100755572</v>
+        <v>72.76713983877357</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>32.9484347022272</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>25.76596849795753</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.27762328278614</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.322054304721958</v>
+        <v>0.3995713156284518</v>
       </c>
       <c r="C2" t="n">
-        <v>4.927391727614741</v>
+        <v>7.639960634448678</v>
       </c>
       <c r="D2" t="n">
-        <v>24.34439782220816</v>
+        <v>8.202502068982101</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.51977080836984</v>
+        <v>2.248202242725196</v>
       </c>
       <c r="C3" t="n">
-        <v>57.39297079026854</v>
+        <v>36.64864179953343</v>
       </c>
       <c r="D3" t="n">
-        <v>108.3947640258903</v>
+        <v>65.62983402889927</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.54792269662352</v>
+        <v>8.091564578402211</v>
       </c>
       <c r="C4" t="n">
-        <v>143.3253473429918</v>
+        <v>96.12880820903068</v>
       </c>
       <c r="D4" t="n">
-        <v>141.1684476367616</v>
+        <v>134.2127651521729</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.04963683122264</v>
+        <v>17.00877897607599</v>
       </c>
       <c r="C5" t="n">
-        <v>153.520797251595</v>
+        <v>241.313585703866</v>
       </c>
       <c r="D5" t="n">
-        <v>89.65810909033996</v>
+        <v>112.5082869066845</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.24536447726626</v>
+        <v>16.26166897314417</v>
       </c>
       <c r="C6" t="n">
-        <v>131.5021597407475</v>
+        <v>350.3906643842079</v>
       </c>
       <c r="D6" t="n">
-        <v>39.64788103600744</v>
+        <v>59.25043744670351</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.18178755620168</v>
+        <v>6.647413705455153</v>
       </c>
       <c r="C7" t="n">
-        <v>105.1010004781423</v>
+        <v>268.1123527866912</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>69.9298889735003</v>
+        <v>112.3217548428776</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>37.05312185368311</v>
+        <v>42.93280885441725</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.988660995905543</v>
+        <v>0.3121957699504857</v>
       </c>
       <c r="C2" t="n">
-        <v>3.566689409528662</v>
+        <v>12.85696793481623</v>
       </c>
       <c r="D2" t="n">
-        <v>22.36813969355933</v>
+        <v>16.54833930278424</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.30669049881928</v>
+        <v>1.811324514335365</v>
       </c>
       <c r="C3" t="n">
-        <v>37.95436624618169</v>
+        <v>33.40396563699772</v>
       </c>
       <c r="D3" t="n">
-        <v>102.9215205747144</v>
+        <v>58.80177874586271</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.42252103238718</v>
+        <v>6.381360077604267</v>
       </c>
       <c r="C4" t="n">
-        <v>143.1083811003533</v>
+        <v>93.7549422601619</v>
       </c>
       <c r="D4" t="n">
-        <v>159.8275445036765</v>
+        <v>135.3741726862969</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.01375413452202</v>
+        <v>15.19254572321939</v>
       </c>
       <c r="C5" t="n">
-        <v>205.4061634210389</v>
+        <v>212.9901644363456</v>
       </c>
       <c r="D5" t="n">
-        <v>114.8399377042707</v>
+        <v>127.5535704742669</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.17494068446774</v>
+        <v>18.87802660496192</v>
       </c>
       <c r="C6" t="n">
-        <v>182.2192461421378</v>
+        <v>365.2032737458838</v>
       </c>
       <c r="D6" t="n">
-        <v>54.58124536530568</v>
+        <v>75.31084814047708</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.12296480940488</v>
+        <v>11.0191362324662</v>
       </c>
       <c r="C7" t="n">
-        <v>144.2069567814055</v>
+        <v>367.404352098805</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>44.43586458961913</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.93590866178347</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>100.5555086074795</v>
+        <v>204.4489594093982</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>57.57655761096267</v>
+        <v>78.76561831172157</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>36.72718161587318</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.637375244234432</v>
+        <v>0.2218749811597791</v>
       </c>
       <c r="C2" t="n">
-        <v>1.727875959474386</v>
+        <v>7.302239424187775</v>
       </c>
       <c r="D2" t="n">
-        <v>15.60193451589031</v>
+        <v>12.17956201888593</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.93991776805847</v>
+        <v>2.449460522095792</v>
       </c>
       <c r="C3" t="n">
-        <v>30.48326621686346</v>
+        <v>43.45215338996383</v>
       </c>
       <c r="D3" t="n">
-        <v>101.5421650502476</v>
+        <v>65.24204368572178</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.06815116888308</v>
+        <v>10.50371868773662</v>
       </c>
       <c r="C4" t="n">
-        <v>140.211243625121</v>
+        <v>133.1917475397563</v>
       </c>
       <c r="D4" t="n">
-        <v>173.0880107449382</v>
+        <v>136.7780719033699</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.73181261695394</v>
+        <v>11.04466167277662</v>
       </c>
       <c r="C5" t="n">
-        <v>249.7566159603886</v>
+        <v>313.6193041216436</v>
       </c>
       <c r="D5" t="n">
-        <v>120.80405500757</v>
+        <v>114.3245201595411</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.99127174831558</v>
+        <v>6.84278149860027</v>
       </c>
       <c r="C6" t="n">
-        <v>211.2809416832519</v>
+        <v>313.5603992593889</v>
       </c>
       <c r="D6" t="n">
-        <v>52.72966919509619</v>
+        <v>62.34981494901069</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.222537933694536</v>
+        <v>3.353650157707104</v>
       </c>
       <c r="C7" t="n">
-        <v>143.4284308519377</v>
+        <v>143.7877505116921</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>71.01472018669303</v>
+        <v>57.99674562838032</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95624762613216</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>25.84843530511426</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.19655482949439</v>
+        <v>23.34596040698915</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.028511741152163</v>
+        <v>0.1286089492563322</v>
       </c>
       <c r="C2" t="n">
-        <v>7.936448441131216</v>
+        <v>4.200898426472102</v>
       </c>
       <c r="D2" t="n">
-        <v>16.56895600457342</v>
+        <v>8.390015880493241</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.52067044061608</v>
+        <v>1.639518666092173</v>
       </c>
       <c r="C3" t="n">
-        <v>18.82501222893259</v>
+        <v>35.83869994352981</v>
       </c>
       <c r="D3" t="n">
-        <v>91.86704142489528</v>
+        <v>60.19586048589318</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.77086154094555</v>
+        <v>7.249225048158448</v>
       </c>
       <c r="C4" t="n">
-        <v>111.1377671115559</v>
+        <v>115.9493126100695</v>
       </c>
       <c r="D4" t="n">
-        <v>181.7794231706351</v>
+        <v>131.8516619234594</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.69655181505907</v>
+        <v>10.30835089459151</v>
       </c>
       <c r="C5" t="n">
-        <v>252.9472959991907</v>
+        <v>255.3525778745954</v>
       </c>
       <c r="D5" t="n">
-        <v>148.8084082712103</v>
+        <v>118.5951226730147</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.66425195181016</v>
+        <v>6.31950997223672</v>
       </c>
       <c r="C6" t="n">
-        <v>293.5150746340775</v>
+        <v>319.4371410170102</v>
       </c>
       <c r="D6" t="n">
-        <v>70.19888784446394</v>
+        <v>65.97246397768143</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>2.515237618280328</v>
       </c>
       <c r="C7" t="n">
-        <v>208.4054026575129</v>
+        <v>190.9185125494687</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28561613314036</v>
+        <v>32.39865598784899</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>116.4941825859265</v>
+        <v>68.17746932141974</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>26.28629478120835</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>48.92343334573128</v>
+        <v>27.17968519207294</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>20.41249826669968</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>15.9435827169682</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>12.43874341280708</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.05884810899257</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.410591524553419</v>
+        <v>0.2061670178918302</v>
       </c>
       <c r="C2" t="n">
-        <v>4.197953183359361</v>
+        <v>7.340527584653401</v>
       </c>
       <c r="D2" t="n">
-        <v>12.46819584393449</v>
+        <v>8.020878743696441</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.99543541884404</v>
+        <v>1.021017612416683</v>
       </c>
       <c r="C3" t="n">
-        <v>24.1755372170777</v>
+        <v>25.2407334761855</v>
       </c>
       <c r="D3" t="n">
-        <v>86.00109889202059</v>
+        <v>53.42671006511142</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.04414725562465</v>
+        <v>5.194427103169875</v>
       </c>
       <c r="C4" t="n">
-        <v>88.13934539187015</v>
+        <v>101.9486085998058</v>
       </c>
       <c r="D4" t="n">
-        <v>185.1104931311446</v>
+        <v>132.0941536064083</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.55620295108078</v>
+        <v>10.77468105410875</v>
       </c>
       <c r="C5" t="n">
-        <v>244.2097414313941</v>
+        <v>234.1713711554705</v>
       </c>
       <c r="D5" t="n">
-        <v>168.3206438931157</v>
+        <v>137.0028921276424</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.27181491201868</v>
+        <v>9.660397409788615</v>
       </c>
       <c r="C6" t="n">
-        <v>339.8447305451887</v>
+        <v>366.0083068633662</v>
       </c>
       <c r="D6" t="n">
-        <v>84.08570912103508</v>
+        <v>84.81023892676923</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>4.671155576806323</v>
       </c>
       <c r="C7" t="n">
-        <v>269.7891778655447</v>
+        <v>319.0159712518883</v>
       </c>
       <c r="D7" t="n">
-        <v>44.31609136970101</v>
+        <v>41.68108053150257</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>154.212929383089</v>
+        <v>154.129480828228</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>52.80624551602742</v>
+        <v>52.91718300660731</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>21.96562313481813</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>12.58404207303562</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.93720920465721</v>
+        <v>0.2415099352447153</v>
       </c>
       <c r="C2" t="n">
-        <v>8.699266407330986</v>
+        <v>18.6070642385898</v>
       </c>
       <c r="D2" t="n">
-        <v>18.74254542177585</v>
+        <v>12.05880705126357</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.90783888898781</v>
+        <v>0.849211764173491</v>
       </c>
       <c r="C3" t="n">
-        <v>20.7443289907351</v>
+        <v>26.69372007847078</v>
       </c>
       <c r="D3" t="n">
-        <v>77.98022014832415</v>
+        <v>48.21362975556086</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.0411609547829</v>
+        <v>3.637375244234433</v>
       </c>
       <c r="C4" t="n">
-        <v>76.34659196845746</v>
+        <v>83.08530821040756</v>
       </c>
       <c r="D4" t="n">
-        <v>184.6510352055571</v>
+        <v>127.8569305148791</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.35985341023141</v>
+        <v>9.596583809012573</v>
       </c>
       <c r="C5" t="n">
-        <v>208.7931930006905</v>
+        <v>212.4502031990098</v>
       </c>
       <c r="D5" t="n">
-        <v>186.6056948847125</v>
+        <v>150.7964473723101</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.26051696565324</v>
+        <v>11.67298020349458</v>
       </c>
       <c r="C6" t="n">
-        <v>359.2460286765141</v>
+        <v>366.6523333573521</v>
       </c>
       <c r="D6" t="n">
-        <v>104.2920403698429</v>
+        <v>103.8090204993535</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.39865598784899</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>355.486916716953</v>
+        <v>413.8763614270321</v>
       </c>
       <c r="D7" t="n">
-        <v>53.35896947351839</v>
+        <v>52.4007837141735</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>3.00414797499524</v>
       </c>
       <c r="C8" t="n">
-        <v>225.8117894538088</v>
+        <v>270.7071119690155</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>99.51092905016091</v>
+        <v>110.9374905798895</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>40.28601704376787</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>14.31977201414398</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.981788761975816</v>
+        <v>3.161227607674729</v>
       </c>
       <c r="C2" t="n">
-        <v>2.978622534684823</v>
+        <v>15.43012866764712</v>
       </c>
       <c r="D2" t="n">
-        <v>11.41281706186917</v>
+        <v>11.65138175400114</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.6471927212769</v>
+        <v>0.1482439033412684</v>
       </c>
       <c r="C2" t="n">
-        <v>5.14926670877452</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D2" t="n">
-        <v>13.94376264341745</v>
+        <v>11.31660578685298</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.39442589739574</v>
+        <v>0.8050331174823845</v>
       </c>
       <c r="C3" t="n">
-        <v>27.93072218582175</v>
+        <v>46.12250714551516</v>
       </c>
       <c r="D3" t="n">
-        <v>85.55931242510952</v>
+        <v>46.55447613538375</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.35718590455915</v>
+        <v>2.692933952749001</v>
       </c>
       <c r="C4" t="n">
-        <v>112.4395645673872</v>
+        <v>75.03203179247099</v>
       </c>
       <c r="D4" t="n">
-        <v>187.2929182776853</v>
+        <v>122.3944862884499</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.89546138392689</v>
+        <v>7.952156404399165</v>
       </c>
       <c r="C5" t="n">
-        <v>308.4405849817417</v>
+        <v>187.2929182776853</v>
       </c>
       <c r="D5" t="n">
-        <v>164.3445656909161</v>
+        <v>158.9694970101648</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.0855762811855</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="C6" t="n">
-        <v>293.9980945045669</v>
+        <v>353.2082802953963</v>
       </c>
       <c r="D6" t="n">
-        <v>80.9863316187279</v>
+        <v>119.3461596667635</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>9.761517423326035</v>
       </c>
       <c r="C7" t="n">
-        <v>158.7594030014559</v>
+        <v>458.6715456764056</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9794497181356</v>
+        <v>64.85719858565703</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>73.35127972280043</v>
+        <v>381.5267928243954</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>195.1390459300257</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>25.73749781453438</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>73.31200981463057</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>14.82929907264807</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.780931393232719</v>
+        <v>3.420409001595887</v>
       </c>
       <c r="C2" t="n">
-        <v>6.069164307653782</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="D2" t="n">
-        <v>12.56931585747191</v>
+        <v>18.31155817961151</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.70872403147496</v>
+        <v>5.105088062083414</v>
       </c>
       <c r="C3" t="n">
-        <v>7.505461198966866</v>
+        <v>30.46363126277852</v>
       </c>
       <c r="D3" t="n">
-        <v>12.72345024703866</v>
+        <v>10.97103059495811</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39850464483496</v>
+        <v>11.67729479609222</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14511255237124</v>
+        <v>59.94344661994008</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57629466409823</v>
+        <v>0.7784863197394816</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.976479112827081</v>
+        <v>1.905572293943059</v>
       </c>
       <c r="C2" t="n">
-        <v>6.608143797285281</v>
+        <v>11.32838675930394</v>
       </c>
       <c r="D2" t="n">
-        <v>22.70193391300324</v>
+        <v>29.45832161362979</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.13426275577033</v>
+        <v>9.385508052599507</v>
       </c>
       <c r="C3" t="n">
-        <v>17.78926840095221</v>
+        <v>38.71031197845173</v>
       </c>
       <c r="D3" t="n">
-        <v>20.20436775339936</v>
+        <v>24.32770811123596</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.77922993973148</v>
+        <v>6.470699118690727</v>
       </c>
       <c r="C4" t="n">
-        <v>12.16287230791373</v>
+        <v>49.27686251926016</v>
       </c>
       <c r="D4" t="n">
-        <v>21.73491242432013</v>
+        <v>20.01194520336698</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44368103498713</v>
+        <v>13.62598587089799</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15948366887557</v>
+        <v>73.74062941897736</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251301270523606</v>
+        <v>1.603057161282117</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.857507714163971</v>
+        <v>1.530544670920778</v>
       </c>
       <c r="C2" t="n">
-        <v>5.922883899721008</v>
+        <v>5.347579745032376</v>
       </c>
       <c r="D2" t="n">
-        <v>30.15438073594078</v>
+        <v>25.69822790636451</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.06415775814131</v>
+        <v>7.804894248762142</v>
       </c>
       <c r="C3" t="n">
-        <v>22.59492341324034</v>
+        <v>42.13170272775187</v>
       </c>
       <c r="D3" t="n">
-        <v>33.6739462556656</v>
+        <v>43.19199024833842</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.31222113214627</v>
+        <v>13.41361888312417</v>
       </c>
       <c r="C4" t="n">
-        <v>31.21761349964007</v>
+        <v>78.32481359251477</v>
       </c>
       <c r="D4" t="n">
-        <v>26.98039040811084</v>
+        <v>28.1162725019244</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.13087554430109</v>
+        <v>6.356816384998099</v>
       </c>
       <c r="C5" t="n">
-        <v>15.06982726018854</v>
+        <v>55.78781329382501</v>
       </c>
       <c r="D5" t="n">
-        <v>30.23782929080177</v>
+        <v>27.36621725587985</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74024873951915</v>
+        <v>14.82949986295102</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1155173110668</v>
+        <v>87.32927697071153</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022074621855745</v>
+        <v>2.471583310491836</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.051893759604838</v>
+        <v>1.519745446174062</v>
       </c>
       <c r="C2" t="n">
-        <v>6.585563600087604</v>
+        <v>11.8516582856675</v>
       </c>
       <c r="D2" t="n">
-        <v>28.37349040043707</v>
+        <v>29.61932823712627</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.04867077905162</v>
+        <v>6.396086293167969</v>
       </c>
       <c r="C3" t="n">
-        <v>22.81090790817464</v>
+        <v>29.3935262651495</v>
       </c>
       <c r="D3" t="n">
-        <v>49.10211142790422</v>
+        <v>53.72614311490671</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.60049510429634</v>
+        <v>14.34529745445439</v>
       </c>
       <c r="C4" t="n">
-        <v>45.06516486804134</v>
+        <v>94.07401026404212</v>
       </c>
       <c r="D4" t="n">
-        <v>36.94807484932871</v>
+        <v>43.41877396801944</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.92443078896878</v>
+        <v>13.54811831860599</v>
       </c>
       <c r="C5" t="n">
-        <v>38.48451000647497</v>
+        <v>105.6115092843506</v>
       </c>
       <c r="D5" t="n">
-        <v>33.25670348136071</v>
+        <v>31.39138284329177</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.83398682699105</v>
+        <v>6.681774875103793</v>
       </c>
       <c r="C6" t="n">
-        <v>18.39500673447249</v>
+        <v>52.40765594810324</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>33.08686112852601</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.40156017323271</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06913587882952</v>
+        <v>16.06040782538856</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8796007333164</v>
+        <v>100.5888700642757</v>
       </c>
       <c r="D21" t="n">
-        <v>6.8834803347922</v>
+        <v>3.381138489555486</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.556912990215199</v>
+        <v>1.156498795602743</v>
       </c>
       <c r="C2" t="n">
-        <v>12.53986342634451</v>
+        <v>7.528041396164542</v>
       </c>
       <c r="D2" t="n">
-        <v>32.37509404294707</v>
+        <v>31.00457424781852</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.57252314249191</v>
+        <v>5.728497854280139</v>
       </c>
       <c r="C3" t="n">
-        <v>22.91890015564179</v>
+        <v>38.57777603837842</v>
       </c>
       <c r="D3" t="n">
-        <v>56.2050560681299</v>
+        <v>63.61725123519331</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.57198336314417</v>
+        <v>13.20941536064083</v>
       </c>
       <c r="C4" t="n">
-        <v>42.99760420289756</v>
+        <v>82.95768100885549</v>
       </c>
       <c r="D4" t="n">
-        <v>45.40975831223197</v>
+        <v>58.31286838914779</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.82563412373834</v>
+        <v>17.59782759862408</v>
       </c>
       <c r="C5" t="n">
-        <v>46.80482179996669</v>
+        <v>139.972678932989</v>
       </c>
       <c r="D5" t="n">
-        <v>31.73499453977815</v>
+        <v>39.41717032550945</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.36354975020759</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="C6" t="n">
-        <v>27.45162930614931</v>
+        <v>110.9738152449467</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>35.30070220160257</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>7.306166415004762</v>
       </c>
       <c r="C7" t="n">
-        <v>15.51063197939536</v>
+        <v>46.53189593818607</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.06335741083136</v>
+        <v>17.31014094436317</v>
       </c>
       <c r="C21" t="n">
-        <v>66.218975726544</v>
+        <v>113.3814231855788</v>
       </c>
       <c r="D21" t="n">
-        <v>5.29751805812352</v>
+        <v>4.327535236090792</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.175193059712438</v>
+        <v>1.352848336452105</v>
       </c>
       <c r="C2" t="n">
-        <v>8.856346040010477</v>
+        <v>17.68618489200629</v>
       </c>
       <c r="D2" t="n">
-        <v>32.54297290037327</v>
+        <v>37.46938288028377</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.37465207459056</v>
+        <v>4.771293842639499</v>
       </c>
       <c r="C3" t="n">
-        <v>39.74114706791089</v>
+        <v>33.57086274671968</v>
       </c>
       <c r="D3" t="n">
-        <v>69.81698798751192</v>
+        <v>71.77066591896308</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.23787034853076</v>
+        <v>11.9586687854304</v>
       </c>
       <c r="C4" t="n">
-        <v>51.71454206890498</v>
+        <v>88.75195595932014</v>
       </c>
       <c r="D4" t="n">
-        <v>63.89017709697393</v>
+        <v>73.44945449322512</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.74128593663113</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="C5" t="n">
-        <v>67.17608666308801</v>
+        <v>146.2558642401686</v>
       </c>
       <c r="D5" t="n">
-        <v>41.96971435655115</v>
+        <v>50.06913291658734</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.70822530985623</v>
+        <v>17.38871533761951</v>
       </c>
       <c r="C6" t="n">
-        <v>55.50703345041042</v>
+        <v>163.38147119305</v>
       </c>
       <c r="D6" t="n">
-        <v>34.49566908412018</v>
+        <v>39.32586778901449</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.61800233205675</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>29.88341836956866</v>
+        <v>98.333813552769</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>38.44720359371359</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>20.27799883121787</v>
+        <v>42.05807164993335</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.286283621340009</v>
+        <v>17.68813293743117</v>
       </c>
       <c r="C21" t="n">
-        <v>75.59519257140259</v>
+        <v>125.5857438557614</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375498168672507</v>
+        <v>5.306439881229353</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.901866287304324</v>
+        <v>1.25271007061893</v>
       </c>
       <c r="C2" t="n">
-        <v>6.169302573486956</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="D2" t="n">
-        <v>27.60576369571606</v>
+        <v>29.78917058996097</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.56194490192345</v>
+        <v>7.127488332831844</v>
       </c>
       <c r="C3" t="n">
-        <v>36.54064955206628</v>
+        <v>58.82632243846888</v>
       </c>
       <c r="D3" t="n">
-        <v>79.64919124554373</v>
+        <v>77.96549393276045</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.52913062152258</v>
+        <v>9.010480429577225</v>
       </c>
       <c r="C4" t="n">
-        <v>79.86910273129502</v>
+        <v>125.8276580102009</v>
       </c>
       <c r="D4" t="n">
-        <v>84.52749558794612</v>
+        <v>66.8511281729823</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.46687960552754</v>
+        <v>9.792933349861935</v>
       </c>
       <c r="C5" t="n">
-        <v>83.42401116837273</v>
+        <v>97.61026549473915</v>
       </c>
       <c r="D5" t="n">
-        <v>55.02695882303374</v>
+        <v>37.89546138392689</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.05919226635785</v>
+        <v>6.601271563355554</v>
       </c>
       <c r="C6" t="n">
-        <v>83.723444218168</v>
+        <v>64.76491430145784</v>
       </c>
       <c r="D6" t="n">
-        <v>40.25165587411923</v>
+        <v>25.318291544821</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.4213339960379</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>56.89227946110266</v>
+        <v>29.52409870981433</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>31.12631096314512</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.07187287105504</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.34153469455343</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.495439101252038</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.26061977674193</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.495439101252038</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
